--- a/90132_REPORT_BOTTEGA_04-01-2026.xlsx
+++ b/90132_REPORT_BOTTEGA_04-01-2026.xlsx
@@ -9,12 +9,13 @@
     <sheet name="VENDUTO FASCIA ORARIA" r:id="rId3" sheetId="1"/>
     <sheet name="ANALISI ARTICOLI" r:id="rId4" sheetId="2"/>
     <sheet name="PDT VENUTI FS GIORNALIERO" r:id="rId5" sheetId="3"/>
+    <sheet name="INGRESSI" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="99">
   <si>
     <t>FASCIA ORARIA</t>
   </si>
@@ -49,6 +50,39 @@
     <t>15:00 - 15:59</t>
   </si>
   <si>
+    <t>16:00 - 16:59</t>
+  </si>
+  <si>
+    <t>17:00 - 17:59</t>
+  </si>
+  <si>
+    <t>18:00 - 18:59</t>
+  </si>
+  <si>
+    <t>19:00 - 19:59</t>
+  </si>
+  <si>
+    <t>20:00 - 20:59</t>
+  </si>
+  <si>
+    <t>21:00 - 21:59</t>
+  </si>
+  <si>
+    <t>22:00 - 22:59</t>
+  </si>
+  <si>
+    <t>23:00 - 23:59</t>
+  </si>
+  <si>
+    <t>0:00 - 0:59</t>
+  </si>
+  <si>
+    <t>1:00 - 1:59</t>
+  </si>
+  <si>
+    <t>2:00 - 2:59</t>
+  </si>
+  <si>
     <t>TOTALE INCASSI 04/01/2026</t>
   </si>
   <si>
@@ -79,40 +113,58 @@
     <t>Fiorentina In Costata Dry Aged</t>
   </si>
   <si>
+    <t>50-001-032-001850</t>
+  </si>
+  <si>
+    <t>Filetto</t>
+  </si>
+  <si>
     <t>50-001-032-001830</t>
   </si>
   <si>
     <t>Gnocchi</t>
   </si>
   <si>
-    <t>50-001-032-001850</t>
-  </si>
-  <si>
-    <t>Filetto</t>
-  </si>
-  <si>
     <t>50-001-032-001930</t>
   </si>
   <si>
     <t>Patate Arrosto</t>
   </si>
   <si>
+    <t>50-001-032-001190</t>
+  </si>
+  <si>
+    <t>Fiorentina In Costata</t>
+  </si>
+  <si>
+    <t>50-001-032-001400</t>
+  </si>
+  <si>
+    <t>Lasagna</t>
+  </si>
+  <si>
+    <t>50-001-032-001490</t>
+  </si>
+  <si>
+    <t>Tagliata Pollo</t>
+  </si>
+  <si>
     <t>50-001-032-001840</t>
   </si>
   <si>
     <t>Controfiletto</t>
   </si>
   <si>
-    <t>50-001-032-001490</t>
-  </si>
-  <si>
-    <t>Tagliata Pollo</t>
-  </si>
-  <si>
-    <t>50-001-032-001400</t>
-  </si>
-  <si>
-    <t>Lasagna</t>
+    <t>50-001-032-001820</t>
+  </si>
+  <si>
+    <t>Ravioli</t>
+  </si>
+  <si>
+    <t>50-001-032-001690</t>
+  </si>
+  <si>
+    <t>CL Chianti buccia nera</t>
   </si>
   <si>
     <t>50-001-032-001480</t>
@@ -121,16 +173,10 @@
     <t>Salsiccie toscane</t>
   </si>
   <si>
-    <t>50-001-032-001820</t>
-  </si>
-  <si>
-    <t>Ravioli</t>
-  </si>
-  <si>
-    <t>50-001-032-001190</t>
-  </si>
-  <si>
-    <t>Fiorentina In Costata</t>
+    <t>50-001-032-000210</t>
+  </si>
+  <si>
+    <t>Acqua Gas 0,75 Var</t>
   </si>
   <si>
     <t>50-001-032-001600</t>
@@ -139,16 +185,10 @@
     <t>BT Primitivo Vallone</t>
   </si>
   <si>
-    <t>50-001-032-000210</t>
-  </si>
-  <si>
-    <t>Acqua Gas 0,75 Var</t>
-  </si>
-  <si>
-    <t>50-001-032-001690</t>
-  </si>
-  <si>
-    <t>CL Chianti buccia nera</t>
+    <t>50-001-032-000230</t>
+  </si>
+  <si>
+    <t>Coca Cola Zero  0,33 Vap</t>
   </si>
   <si>
     <t>50-001-032-001950</t>
@@ -163,10 +203,22 @@
     <t>Caesar Salad</t>
   </si>
   <si>
-    <t>50-001-032-000230</t>
-  </si>
-  <si>
-    <t>Coca Cola Zero  0,33 Vap</t>
+    <t>50-001-032-001920</t>
+  </si>
+  <si>
+    <t>Insalata Greca</t>
+  </si>
+  <si>
+    <t>50-001-032-001940</t>
+  </si>
+  <si>
+    <t>Fagioli All'Olio</t>
+  </si>
+  <si>
+    <t>50-001-032-001620</t>
+  </si>
+  <si>
+    <t>BT Morellino</t>
   </si>
   <si>
     <t>50-001-032-001380</t>
@@ -175,10 +227,10 @@
     <t>Battuta al Coltello</t>
   </si>
   <si>
-    <t>50-001-032-001920</t>
-  </si>
-  <si>
-    <t>Insalata Greca</t>
+    <t>50-001-032-001150</t>
+  </si>
+  <si>
+    <t>Hamburger E Patate</t>
   </si>
   <si>
     <t>50-001-032-000040</t>
@@ -211,12 +263,6 @@
     <t>CL Umberto</t>
   </si>
   <si>
-    <t>50-001-032-001940</t>
-  </si>
-  <si>
-    <t>Fagioli All'Olio</t>
-  </si>
-  <si>
     <t>50-001-032-000290</t>
   </si>
   <si>
@@ -251,6 +297,21 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>16:00-18:59</t>
+  </si>
+  <si>
+    <t>19:00-02:59</t>
+  </si>
+  <si>
+    <t>04/01/2026</t>
+  </si>
+  <si>
+    <t>VAR %</t>
+  </si>
+  <si>
+    <t>05/01/2025</t>
   </si>
 </sst>
 </file>
@@ -388,7 +449,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true"/>
@@ -401,13 +462,27 @@
     <xf numFmtId="4" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.59375" customWidth="true" bestFit="true"/>
@@ -495,27 +570,115 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s" s="1">
+      <c r="A11" t="s" s="2">
         <v>11</v>
       </c>
-      <c r="B11" t="n" s="1">
-        <v>1737.64</v>
+      <c r="B11" t="n" s="5">
+        <v>164.9091</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s" s="1">
+      <c r="A12" t="s" s="4">
         <v>12</v>
       </c>
-      <c r="B12" t="n" s="1">
-        <v>1859.99</v>
+      <c r="B12" t="n" s="7">
+        <v>0.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s" s="1">
+      <c r="A13" t="s" s="2">
         <v>13</v>
       </c>
-      <c r="B13" t="n" s="1">
-        <v>-6.58</v>
+      <c r="B13" t="n" s="5">
+        <v>88.0453</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="4">
+        <v>14</v>
+      </c>
+      <c r="B14" t="n" s="7">
+        <v>109.6544</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B15" t="n" s="5">
+        <v>117.2727</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="4">
+        <v>16</v>
+      </c>
+      <c r="B16" t="n" s="7">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B17" t="n" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="4">
+        <v>18</v>
+      </c>
+      <c r="B18" t="n" s="7">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B19" t="n" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="4">
+        <v>20</v>
+      </c>
+      <c r="B20" t="n" s="7">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B21" t="n" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="1">
+        <v>22</v>
+      </c>
+      <c r="B22" t="n" s="1">
+        <v>2217.52</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="1">
+        <v>23</v>
+      </c>
+      <c r="B23" t="n" s="1">
+        <v>2608.45</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="B24" t="n" s="1">
+        <v>-14.99</v>
       </c>
     </row>
   </sheetData>
@@ -525,7 +688,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.359375" customWidth="true" bestFit="true"/>
@@ -537,492 +700,526 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="4">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C2" t="n" s="7">
-        <v>380.6363</v>
+        <v>450.4999</v>
       </c>
       <c r="D2" t="n" s="7">
-        <v>7.9</v>
+        <v>9.35</v>
       </c>
       <c r="E2" t="n" s="7">
-        <v>21.91</v>
+        <v>20.32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C3" t="n" s="5">
-        <v>203.6363</v>
+        <v>209.9999</v>
       </c>
       <c r="D3" t="n" s="5">
-        <v>16.0</v>
+        <v>11.0</v>
       </c>
       <c r="E3" t="n" s="5">
-        <v>11.72</v>
+        <v>9.47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="4">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C4" t="n" s="7">
-        <v>133.6363</v>
+        <v>203.6363</v>
       </c>
       <c r="D4" t="n" s="7">
-        <v>7.0</v>
+        <v>16.0</v>
       </c>
       <c r="E4" t="n" s="7">
-        <v>7.69</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C5" t="n" s="5">
-        <v>114.5454</v>
+        <v>141.818</v>
       </c>
       <c r="D5" t="n" s="5">
-        <v>21.0</v>
+        <v>26.0</v>
       </c>
       <c r="E5" t="n" s="5">
-        <v>6.59</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s" s="4">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C6" t="n" s="7">
-        <v>90.909</v>
+        <v>119.3818</v>
       </c>
       <c r="D6" t="n" s="7">
-        <v>5.0</v>
+        <v>2.68</v>
       </c>
       <c r="E6" t="n" s="7">
-        <v>5.23</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C7" t="n" s="5">
-        <v>82.0909</v>
+        <v>95.4546</v>
       </c>
       <c r="D7" t="n" s="5">
         <v>7.0</v>
       </c>
       <c r="E7" t="n" s="5">
-        <v>4.72</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="4">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s" s="4">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C8" t="n" s="7">
-        <v>81.8182</v>
+        <v>93.8182</v>
       </c>
       <c r="D8" t="n" s="7">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="E8" t="n" s="7">
-        <v>4.71</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n" s="5">
-        <v>79.2728</v>
+        <v>90.909</v>
       </c>
       <c r="D9" t="n" s="5">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="E9" t="n" s="5">
-        <v>4.56</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="4">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s" s="4">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n" s="7">
-        <v>76.3636</v>
+        <v>89.0909</v>
       </c>
       <c r="D10" t="n" s="7">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="E10" t="n" s="7">
-        <v>4.39</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n" s="5">
-        <v>57.9091</v>
+        <v>80.0</v>
       </c>
       <c r="D11" t="n" s="5">
-        <v>1.3</v>
+        <v>16.0</v>
       </c>
       <c r="E11" t="n" s="5">
-        <v>3.33</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="4">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s" s="4">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C12" t="n" s="7">
-        <v>54.5454</v>
+        <v>79.2728</v>
       </c>
       <c r="D12" t="n" s="7">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="E12" t="n" s="7">
-        <v>3.14</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C13" t="n" s="5">
-        <v>50.9091</v>
+        <v>76.3636</v>
       </c>
       <c r="D13" t="n" s="5">
-        <v>16.0</v>
+        <v>24.0</v>
       </c>
       <c r="E13" t="n" s="5">
-        <v>2.93</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="4">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s" s="4">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C14" t="n" s="7">
-        <v>50.0</v>
+        <v>72.7272</v>
       </c>
       <c r="D14" t="n" s="7">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="E14" t="n" s="7">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C15" t="n" s="5">
-        <v>44.5454</v>
+        <v>54.0909</v>
       </c>
       <c r="D15" t="n" s="5">
-        <v>7.0</v>
+        <v>17.0</v>
       </c>
       <c r="E15" t="n" s="5">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="4">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s" s="4">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C16" t="n" s="7">
-        <v>40.9091</v>
+        <v>50.909</v>
       </c>
       <c r="D16" t="n" s="7">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="E16" t="n" s="7">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C17" t="n" s="5">
-        <v>31.8182</v>
+        <v>40.9091</v>
       </c>
       <c r="D17" t="n" s="5">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="E17" t="n" s="5">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="4">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s" s="4">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C18" t="n" s="7">
-        <v>29.091</v>
+        <v>35.4546</v>
       </c>
       <c r="D18" t="n" s="7">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="E18" t="n" s="7">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C19" t="n" s="5">
-        <v>23.6364</v>
+        <v>31.8181</v>
       </c>
       <c r="D19" t="n" s="5">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="E19" t="n" s="5">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="4">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B20" t="s" s="4">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C20" t="n" s="7">
-        <v>21.8182</v>
+        <v>30.0</v>
       </c>
       <c r="D20" t="n" s="7">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="E20" t="n" s="7">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C21" t="n" s="5">
-        <v>20.9091</v>
+        <v>29.091</v>
       </c>
       <c r="D21" t="n" s="5">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E21" t="n" s="5">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="4">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s" s="4">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C22" t="n" s="7">
-        <v>19.0909</v>
+        <v>27.2727</v>
       </c>
       <c r="D22" t="n" s="7">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="E22" t="n" s="7">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="C23" t="n" s="5">
-        <v>16.3636</v>
+        <v>21.8182</v>
       </c>
       <c r="D23" t="n" s="5">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="E23" t="n" s="5">
-        <v>0.94</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="4">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="B24" t="s" s="4">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C24" t="n" s="7">
-        <v>15.0</v>
+        <v>20.9091</v>
       </c>
       <c r="D24" t="n" s="7">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="E24" t="n" s="7">
-        <v>0.86</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C25" t="n" s="5">
-        <v>6.3636</v>
+        <v>19.0909</v>
       </c>
       <c r="D25" t="n" s="5">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="E25" t="n" s="5">
-        <v>0.37</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="4">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B26" t="s" s="4">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C26" t="n" s="7">
-        <v>5.4546</v>
+        <v>16.3636</v>
       </c>
       <c r="D26" t="n" s="7">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="E26" t="n" s="7">
-        <v>0.31</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C27" t="n" s="5">
-        <v>3.1818</v>
+        <v>15.0</v>
       </c>
       <c r="D27" t="n" s="5">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="E27" t="n" s="5">
-        <v>0.18</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="4">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="B28" t="s" s="4">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="C28" t="n" s="7">
+        <v>12.2728</v>
+      </c>
+      <c r="D28" t="n" s="7">
+        <v>9.0</v>
+      </c>
+      <c r="E28" t="n" s="7">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C29" t="n" s="5">
+        <v>6.3636</v>
+      </c>
+      <c r="D29" t="n" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="E29" t="n" s="5">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="4">
+        <v>86</v>
+      </c>
+      <c r="B30" t="s" s="4">
+        <v>87</v>
+      </c>
+      <c r="C30" t="n" s="7">
         <v>3.1818</v>
       </c>
-      <c r="D28" t="n" s="7">
+      <c r="D30" t="n" s="7">
         <v>1.0</v>
       </c>
-      <c r="E28" t="n" s="7">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="1">
-        <v>73</v>
-      </c>
-      <c r="B29" s="2"/>
-      <c r="C29" t="n" s="1">
-        <v>1737.64</v>
-      </c>
-      <c r="D29" t="n" s="1">
-        <v>160.2</v>
-      </c>
-      <c r="E29" t="n" s="1">
+      <c r="E30" t="n" s="7">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="1">
+        <v>88</v>
+      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" t="n" s="1">
+        <v>2217.52</v>
+      </c>
+      <c r="D31" t="n" s="1">
+        <v>212.03</v>
+      </c>
+      <c r="E31" t="n" s="1">
         <v>100.0</v>
       </c>
     </row>
@@ -1033,7 +1230,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.359375" customWidth="true" bestFit="true"/>
@@ -1044,13 +1241,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -1058,26 +1255,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="1">
-        <v>74</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
       <c r="A5" t="s" s="1">
-        <v>76</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s" s="4">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C6" t="n" s="7">
         <v>21.0</v>
@@ -1088,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C7" t="n" s="5">
         <v>16.0</v>
@@ -1102,10 +1299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="4">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B8" t="s" s="4">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n" s="7">
         <v>16.0</v>
@@ -1116,10 +1313,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n" s="5">
         <v>10.0</v>
@@ -1130,10 +1327,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="4">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B10" t="s" s="4">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n" s="7">
         <v>10.0</v>
@@ -1144,10 +1341,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="C11" t="n" s="5">
         <v>8.0</v>
@@ -1158,10 +1355,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="4">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s" s="4">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n" s="7">
         <v>7.9</v>
@@ -1172,10 +1369,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C13" t="n" s="5">
         <v>7.0</v>
@@ -1186,10 +1383,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="4">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s" s="4">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C14" t="n" s="7">
         <v>7.0</v>
@@ -1200,10 +1397,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C15" t="n" s="5">
         <v>7.0</v>
@@ -1214,10 +1411,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="4">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s" s="4">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C16" t="n" s="7">
         <v>6.0</v>
@@ -1228,10 +1425,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C17" t="n" s="5">
         <v>6.0</v>
@@ -1242,10 +1439,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="4">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="B18" t="s" s="4">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="C18" t="n" s="7">
         <v>6.0</v>
@@ -1256,10 +1453,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="C19" t="n" s="5">
         <v>5.0</v>
@@ -1270,10 +1467,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="4">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="B20" t="s" s="4">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C20" t="n" s="7">
         <v>4.0</v>
@@ -1284,10 +1481,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C21" t="n" s="5">
         <v>3.0</v>
@@ -1298,10 +1495,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="4">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B22" t="s" s="4">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="C22" t="n" s="7">
         <v>3.0</v>
@@ -1312,10 +1509,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="C23" t="n" s="5">
         <v>3.0</v>
@@ -1326,10 +1523,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="4">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="B24" t="s" s="4">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="C24" t="n" s="7">
         <v>3.0</v>
@@ -1340,10 +1537,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C25" t="n" s="5">
         <v>2.0</v>
@@ -1354,10 +1551,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="4">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B26" t="s" s="4">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C26" t="n" s="7">
         <v>2.0</v>
@@ -1368,10 +1565,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="C27" t="n" s="5">
         <v>2.0</v>
@@ -1382,10 +1579,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28" t="s" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C28" t="n" s="7">
         <v>1.3</v>
@@ -1396,10 +1593,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="C29" t="n" s="5">
         <v>1.0</v>
@@ -1410,10 +1607,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="4">
+        <v>64</v>
+      </c>
+      <c r="B30" t="s" s="4">
         <v>65</v>
-      </c>
-      <c r="B30" t="s" s="4">
-        <v>66</v>
       </c>
       <c r="C30" t="n" s="7">
         <v>1.0</v>
@@ -1424,10 +1621,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="C31" t="n" s="5">
         <v>1.0</v>
@@ -1438,10 +1635,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="4">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="B32" t="s" s="4">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C32" t="n" s="7">
         <v>1.0</v>
@@ -1452,10 +1649,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="1">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="C33" t="n" s="1">
         <v>160.2</v>
@@ -1465,13 +1662,417 @@
       </c>
     </row>
     <row r="34"/>
+    <row r="35">
+      <c r="A35" t="s" s="1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="4">
+        <v>48</v>
+      </c>
+      <c r="B36" t="s" s="4">
+        <v>49</v>
+      </c>
+      <c r="C36" t="n" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="D36" t="n" s="7">
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="C37" t="n" s="5">
+        <v>5.0</v>
+      </c>
+      <c r="D37" t="n" s="5">
+        <v>6.8182</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="4">
+        <v>64</v>
+      </c>
+      <c r="B38" t="s" s="4">
+        <v>65</v>
+      </c>
+      <c r="C38" t="n" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="D38" t="n" s="7">
+        <v>25.4545</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="C39" t="n" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="D39" t="n" s="5">
+        <v>57.2727</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="4">
+        <v>36</v>
+      </c>
+      <c r="B40" t="s" s="4">
+        <v>37</v>
+      </c>
+      <c r="C40" t="n" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="D40" t="n" s="7">
+        <v>16.3636</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="C41" t="n" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="D41" t="n" s="5">
+        <v>9.5454</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="4">
+        <v>30</v>
+      </c>
+      <c r="B42" t="s" s="4">
+        <v>31</v>
+      </c>
+      <c r="C42" t="n" s="7">
+        <v>1.45</v>
+      </c>
+      <c r="D42" t="n" s="7">
+        <v>69.8636</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="C43" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D43" t="n" s="5">
+        <v>12.7273</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="4">
+        <v>62</v>
+      </c>
+      <c r="B44" t="s" s="4">
+        <v>63</v>
+      </c>
+      <c r="C44" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="D44" t="n" s="7">
+        <v>11.8182</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="C45" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D45" t="n" s="5">
+        <v>11.7273</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="4">
+        <v>84</v>
+      </c>
+      <c r="B46" t="s" s="4">
+        <v>85</v>
+      </c>
+      <c r="C46" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="D46" t="n" s="7">
+        <v>3.1818</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="C47" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D47" t="n" s="5">
+        <v>3.1818</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="1">
+        <v>92</v>
+      </c>
+      <c r="B48" t="s" s="4">
+        <v>93</v>
+      </c>
+      <c r="C48" t="n" s="1">
+        <v>29.45</v>
+      </c>
+      <c r="D48" t="n" s="1">
+        <v>252.95</v>
+      </c>
+    </row>
+    <row r="49"/>
+    <row r="50">
+      <c r="A50" t="s" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="C51" t="n" s="5">
+        <v>6.0</v>
+      </c>
+      <c r="D51" t="n" s="5">
+        <v>19.0909</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="4">
+        <v>52</v>
+      </c>
+      <c r="B52" t="s" s="4">
+        <v>53</v>
+      </c>
+      <c r="C52" t="n" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="D52" t="n" s="7">
+        <v>15.9091</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="C53" t="n" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="D53" t="n" s="5">
+        <v>27.2727</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="4">
+        <v>36</v>
+      </c>
+      <c r="B54" t="s" s="4">
+        <v>37</v>
+      </c>
+      <c r="C54" t="n" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="D54" t="n" s="7">
+        <v>10.909</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C55" t="n" s="5">
+        <v>1.38</v>
+      </c>
+      <c r="D55" t="n" s="5">
+        <v>61.4727</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="4">
+        <v>66</v>
+      </c>
+      <c r="B56" t="s" s="4">
+        <v>67</v>
+      </c>
+      <c r="C56" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="D56" t="n" s="7">
+        <v>30.0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="C57" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D57" t="n" s="5">
+        <v>19.0909</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="4">
+        <v>54</v>
+      </c>
+      <c r="B58" t="s" s="4">
+        <v>55</v>
+      </c>
+      <c r="C58" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="D58" t="n" s="7">
+        <v>18.1818</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="C59" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D59" t="n" s="5">
+        <v>13.6364</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="4">
+        <v>58</v>
+      </c>
+      <c r="B60" t="s" s="4">
+        <v>59</v>
+      </c>
+      <c r="C60" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="D60" t="n" s="7">
+        <v>6.3636</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="C61" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D61" t="n" s="5">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="1">
+        <v>92</v>
+      </c>
+      <c r="B62" t="s" s="4">
+        <v>93</v>
+      </c>
+      <c r="C62" t="n" s="1">
+        <v>22.38</v>
+      </c>
+      <c r="D62" t="n" s="1">
+        <v>226.93</v>
+      </c>
+    </row>
+    <row r="63"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="8">
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="A62:B62"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="12.73046875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="7.9140625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.73046875" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>96</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>97</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n" s="9">
+        <v>8852.0</v>
+      </c>
+      <c r="B2" s="12" t="n">
+        <f>(A2-C2)/C2</f>
+        <v>0.0</v>
+      </c>
+      <c r="C2" t="n" s="9">
+        <v>9397.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>